--- a/data/trans_bre/IP07_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP07_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,96</t>
+          <t>10,4</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 8,85</t>
+          <t>-8,65; 8,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 8,18</t>
+          <t>-8,03; 8,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 11,7</t>
+          <t>-2,26; 12,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 26,41</t>
+          <t>-0,43; 25,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 13,23</t>
+          <t>-11,44; 12,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 11,4</t>
+          <t>-9,88; 11,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 15,06</t>
+          <t>-2,59; 15,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 50,05</t>
+          <t>-0,54; 45,03</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,29</t>
+          <t>1,66</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-1,71%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 6,24</t>
+          <t>-6,8; 6,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 6,81</t>
+          <t>-7,45; 6,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 5,63</t>
+          <t>-4,51; 6,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 5,89</t>
+          <t>-5,65; 9,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 9,15</t>
+          <t>-9,07; 9,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 10,09</t>
+          <t>-10,08; 9,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 6,89</t>
+          <t>-5,12; 7,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 8,11</t>
+          <t>-7,28; 13,17</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,55</t>
+          <t>-0,43</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>-0,54%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 4,01</t>
+          <t>-9,88; 4,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 5,34</t>
+          <t>-10,26; 4,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 9,76</t>
+          <t>-2,9; 9,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 14,39</t>
+          <t>-7,8; 7,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 4,97</t>
+          <t>-11,54; 5,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 7,07</t>
+          <t>-12,42; 6,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 12,19</t>
+          <t>-3,33; 12,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 19,57</t>
+          <t>-9,3; 10,67</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-6,29</t>
+          <t>-6,77</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-7,73%</t>
+          <t>-8,33%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 10,77</t>
+          <t>-1,83; 10,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 11,89</t>
+          <t>-3,9; 10,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 3,78</t>
+          <t>-7,23; 3,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 1,3</t>
+          <t>-14,11; 0,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 13,96</t>
+          <t>-2,19; 13,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 17,59</t>
+          <t>-5,07; 16,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 4,35</t>
+          <t>-7,87; 4,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 1,55</t>
+          <t>-16,66; 1,03</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,21</t>
+          <t>0,7</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 4,74</t>
+          <t>-2,71; 4,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 4,26</t>
+          <t>-3,11; 4,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 3,89</t>
+          <t>-1,7; 4,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 6,54</t>
+          <t>-3,72; 5,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 6,4</t>
+          <t>-3,43; 5,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 5,83</t>
+          <t>-4,09; 6,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 4,62</t>
+          <t>-1,92; 4,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 8,92</t>
+          <t>-4,79; 7,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP07_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP07_R-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,02</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,83%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15,79%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.3353149758343443</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.4412008661261124</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>4.01847216220933</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>10.40021087958464</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.004711873049143068</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.005665754515908279</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.04834175022096716</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.1578543491950419</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-8,65; 8,53</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-8,03; 8,42</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-2,26; 12,13</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-0,43; 25,04</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-11,44; 12,86</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-9,88; 11,4</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-2,59; 15,74</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-0,54; 45,03</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-8.647567588405595</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-8.031374538663751</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.264594447461189</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-0.425447037985013</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.1143878289778945</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.09876945779804555</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.02586709214645724</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.005417158730243789</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>8.530833540096463</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.41959122387866</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>12.13151217018289</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>25.04299110711493</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1285828857618605</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.113989882150063</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.1573518836213026</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.4503234343397075</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,2</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,74</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,41</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,66</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-1,04%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-6,8; 6,63</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-7,45; 6,37</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,51; 6,13</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-5,65; 9,1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-9,07; 9,54</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-10,08; 9,21</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-5,12; 7,4</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-7,28; 13,17</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.1997896987066872</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.742052681028571</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.4085438070913106</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.658193112287931</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.002741168313199181</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.01039061270727599</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.004768565243819034</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.02237710703699653</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,22</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,12</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,33</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-3,87%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-2,67%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-0,54%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-6.798547780574533</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-7.445322006856807</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.513747925703633</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-5.648585440173819</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.09073199104640467</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1007875383211588</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.05119859900447562</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.07282261846575777</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-9,88; 4,37</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-10,26; 4,89</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-2,9; 9,77</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-7,8; 7,97</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-11,54; 5,37</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-12,42; 6,5</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-3,33; 12,1</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-9,3; 10,67</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>6.630360825871996</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>6.369941049100775</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6.133440733366653</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>9.104485814696021</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.09542396012521108</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.09211541596075598</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.07403044947087047</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.1316723945556634</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>4,39</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4,05</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,44</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-6,77</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-1,62%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-8,33%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-3.219693493577125</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.117524917692404</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>3.330446990168501</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.4338232429852318</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.0387407644144394</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.02667231151300569</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.03934910534976336</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.005437471080417794</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,83; 10,46</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,9; 10,97</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-7,23; 3,72</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-14,11; 0,86</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-2,19; 13,7</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-5,07; 16,11</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-7,87; 4,37</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-16,66; 1,03</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-9.875683421627564</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-10.26070383766337</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.895012645294443</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-7.800976380351645</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.1153533940037816</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1242091163155886</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.03331481541415088</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.0929765991854926</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.367449828856262</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.88985112952449</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.771935983233398</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>7.974433840878854</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.05374330597011424</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.06498846983319996</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.1210310829398773</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.1067355857686774</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>4.388438529465843</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>4.047579599054185</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.441309491349207</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-6.76935411309505</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.05488462148295258</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.05607276523456858</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.01616158704175517</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.08327588337019608</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.828138091501797</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.904886881809774</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-7.227910163077839</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-14.11293080019282</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.02194533073000758</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.05074151034595147</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.07867204663876794</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.1665827644134708</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>10.45747748614232</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>10.96597297860418</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.724643609669651</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.8563895204201604</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1370492222801726</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1610567649496841</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.04368895685237514</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.01030982095767924</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,92</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,52</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,7</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,71; 4,39</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,11; 4,57</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,7; 4,19</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-3,72; 5,41</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-3,43; 5,86</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-4,09; 6,2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-1,92; 4,96</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-4,79; 7,4</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.918125810755166</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.5241637162469059</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.284255026577197</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.6996279087426616</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.01197319774357711</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.007014647894300203</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.01494969563068265</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.00923876211332811</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.709859292246793</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.112594480507652</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.702993962960095</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-3.724240720672744</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.034295424197844</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.04088113669299741</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.0191666009111353</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.04791329072694978</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>4.393430354182155</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>4.567908436957992</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.193498727192062</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>5.407113254850348</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.05863033773966098</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.06204167827054349</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.04959591304471775</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.07402314849504189</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
